--- a/results/Int Task Remove ACC 0.9/Rando_fi_all.xlsx
+++ b/results/Int Task Remove ACC 0.9/Rando_fi_all.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.003192534381139522 +/- 0.001704966105865416</t>
+          <t>-9.823182711193867e-05 +/- 0.0015960782720306373</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -886,157 +886,157 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.001669941060903768 +/- 0.001145570116865491</t>
+          <t>-0.009528487229862447 +/- 0.0011664383189624614</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0006876227897839148 +/- 0.0009370719070893365</t>
+          <t>0.002701375245579618 +/- 0.0007995491451915227</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.0020628683693516225 +/- 0.0013324813326375832</t>
+          <t>-0.0034872298624753937 +/- 0.0009175609868501742</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.005795677799607124 +/- 0.0009267172035419195</t>
+          <t>0.004715127701375288 +/- 0.0008840864440078761</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.001964636542239717 +/- 0.0013717328137297655</t>
+          <t>0.0019646365422397506 +/- 0.0011200151523567032</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0007367387033399009 +/- 0.00024557956777992995</t>
+          <t>4.911591355600819e-05 +/- 0.0002644972891519934</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.010068762278978427 +/- 0.0011466225471442892</t>
+          <t>0.0019646365422397506 +/- 0.001280786327151782</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.008447937131630678 +/- 0.002081495098272817</t>
+          <t>-0.0004420432220038739 +/- 0.0015130571513506193</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.008349705304518706 +/- 0.0027346583314489226</t>
+          <t>-0.007760314341846719 +/- 0.0020346085635764297</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-0.0025049115913555854 +/- 0.001431120067223339</t>
+          <t>-0.0017190569744596873 +/- 0.001285486476257599</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.005746561886051127 +/- 0.001121091572741986</t>
+          <t>0.005206286836935225 +/- 0.0012845478222614898</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.004764243614931274 +/- 0.002141476361158316</t>
+          <t>0.004223968565815373 +/- 0.0015869837349119327</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-0.016944990176817266 +/- 0.002428631692549324</t>
+          <t>-0.028143418467583448 +/- 0.0019405448197581925</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-0.006385068762278945 +/- 0.002272108743854692</t>
+          <t>-0.017190569744597217 +/- 0.002494778997878244</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.006777996070726955 +/- 0.0017127304296819987</t>
+          <t>0.0011787819253438858 +/- 0.000735099683059703</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.004273084479371336 +/- 0.0007934918674559513</t>
+          <t>-0.0009823182711198087 +/- 0.0010302640944696738</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.004469548133595324 +/- 0.0013796239592522921</t>
+          <t>-0.0026522593320235212 +/- 0.0011243146505166839</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.011001964636542261 +/- 0.0023162723227016825</t>
+          <t>0.0014734774066798018 +/- 0.0016437328615600663</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.0008349705304518951 +/- 0.00044204322200393063</t>
+          <t>0.00014734774066799128 +/- 0.00022507739169726432</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.007023575638506907 +/- 0.0027174020026764405</t>
+          <t>-0.0007858546168958314 +/- 0.0008277160877383408</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>-0.0005402750491158792 +/- 0.0009933078789860685</t>
+          <t>0.0016699410609037901 +/- 0.0008563652148410003</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.00039292730844798786 +/- 0.0007218535587769667</t>
+          <t>0.00034381139489199076 +/- 0.0011210915727419798</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>-0.0021611001964636166 +/- 0.0015869837349119355</t>
+          <t>-0.0023084479371315637 +/- 0.0010077742892280475</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.005500982318271086 +/- 0.0017681728880157245</t>
+          <t>-0.0009332023575638005 +/- 0.0008055608775469884</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.0005893909626719429 +/- 0.00019646365422394397</t>
+          <t>2.2204460492503132e-17 +/- 0.00031063631239374665</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>-0.007269155206286804 +/- 0.0018612274382609454</t>
+          <t>-0.00702357563850683 +/- 0.0012435156091524717</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.0022102161100197026 +/- 0.0009122876041751875</t>
+          <t>0.002554027504911649 +/- 0.0011787819253437943</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>-0.0020628683693516446 +/- 0.001640794998869358</t>
+          <t>0.0032907662082515055 +/- 0.0009587043858518005</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-4.911591355594158e-05 +/- 0.0008908819816904139</t>
+          <t>0.000540275049115968 +/- 0.0008633789701005614</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>9.823182711199419e-05 +/- 0.00019646365422398837</t>
+          <t>0.000540275049115957 +/- 0.00046335860177097737</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-4.911591355596379e-05 +/- 0.00046335860177093265</t>
+          <t>-0.0004420432220039072 +/- 0.0006752321750917074</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -1046,122 +1046,122 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.005599214145383146 +/- 0.001813967123047096</t>
+          <t>0.0023084479371316634 +/- 0.001099362931512735</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.0013752455795678297 +/- 0.0010017720065997827</t>
+          <t>0.004420432220039361 +/- 0.0008507125773914088</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>-4.911591355598599e-05 +/- 0.00014734774066795797</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.0013752455795678076 +/- 0.0005727850584327604</t>
+          <t>-0.0005893909626718763 +/- 0.0005727850584327375</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.0021611001964636943 +/- 0.0010579891566079684</t>
+          <t>-0.003880157170923315 +/- 0.001150822643797647</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0.004518664047151311 +/- 0.0012190249161091174</t>
+          <t>0.001719056974459765 +/- 0.0007687856504174265</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0.00039292730844796563 +/- 0.0005289945783039786</t>
+          <t>0.00029469548133599367 +/- 0.0005008860032999028</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.0012770137524557468 +/- 0.000666240666318787</t>
+          <t>0.000540275049115957 +/- 0.0009175609868501711</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-9.823182711196087e-05 +/- 0.0007545329811265615</t>
+          <t>-0.001571709233791707 +/- 0.0007218535587769623</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>-0.00240667976424358 +/- 0.0017358150340935493</t>
+          <t>-0.004616895874263238 +/- 0.00124642215525045</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.0031434184675835364 +/- 0.0011455701168654967</t>
+          <t>-0.005206286836935114 +/- 0.0011664383189624596</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>-0.017976424361493094 +/- 0.002367774222631432</t>
+          <t>-0.02794695481335948 +/- 0.0018436467955917134</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-0.00486247544204319 +/- 0.0008349705304518545</t>
+          <t>-0.0006385068762278622 +/- 0.00098354540248039</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-0.0004911591355599044 +/- 0.0009823182711198198</t>
+          <t>-0.0036836935166993713 +/- 0.0013935423339008963</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.000540275049115957 +/- 0.0005127851919897442</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>-0.0020137524557956366 +/- 0.0013970002606412517</t>
+          <t>-0.0021119842829076087 +/- 0.0011424070088028558</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>4.91159135560193e-05 +/- 0.0007750360431266797</t>
+          <t>0.0049607072691552736 +/- 0.0012512513951725968</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.004715127701375288 +/- 0.0015090659622531667</t>
+          <t>-0.00427308447937127 +/- 0.0016148607291526069</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.0012278978388998497 +/- 0.002231938657662428</t>
+          <t>-0.00820235756385066 +/- 0.0020375705808144897</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-0.00024557956777992995 +/- 0.00039598515463155117</t>
+          <t>4.91159135560304e-05 +/- 0.0004079874195932227</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0.0007367387033399009 +/- 0.000503288348033381</t>
+          <t>0.0009823182711199085 +/- 0.0003804502304722367</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>-0.005451866404715089 +/- 0.0008908819816904065</t>
+          <t>-0.009577603143418434 +/- 0.0007995491451915229</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0.006777996070726966 +/- 0.0020814950982727823</t>
+          <t>-0.009675834970530406 +/- 0.002872756152434128</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0.002897838899803562 +/- 0.0010636742547990114</t>
+          <t>0.005058939096267234 +/- 0.0015383555759691252</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1171,42 +1171,42 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>-0.00024557956777991884 +/- 0.0005491326074410149</t>
+          <t>4.91159135560193e-05 +/- 0.00046335860177096203</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0.003438113948919497 +/- 0.0011828678368165312</t>
+          <t>-0.0029469548133594812 +/- 0.0007285067276125241</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>-0.002455795677799566 +/- 0.0009823182711198475</t>
+          <t>0.001669941060903768 +/- 0.0016612509356864267</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.0009823182711198642 +/- 0.0004393060859528144</t>
+          <t>-0.00029469548133589376 +/- 0.00039292730844793234</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.00019646365422399948 +/- 0.0006289905930680505</t>
+          <t>-0.004027504911591306 +/- 0.0007218535587769895</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0.0010314341846758724 +/- 0.001497028551486079</t>
+          <t>0.0034381139489194855 +/- 0.0013717328137297458</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-0.036444007858546124 +/- 0.0011990722608775537</t>
+          <t>-0.03644400785854611 +/- 0.0022805867910105663</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-0.0011787819253437526 +/- 0.0007350996830597016</t>
+          <t>0.0005893909626719651 +/- 0.0006515962260030493</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1216,47 +1216,47 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.004469548133595314 +/- 0.00119200993118974</t>
+          <t>-0.005451866404715078 +/- 0.0009434858896021004</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.0029469548133595814 +/- 0.0008218664307800116</t>
+          <t>-0.0030943025540274395 +/- 0.0005832191594812476</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.0022102161100197026 +/- 0.0008291720538376437</t>
+          <t>-0.0004420432220038961 +/- 0.0008908819816904187</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.0004420432220039627 +/- 0.001212078848649623</t>
+          <t>-0.00397838899803532 +/- 0.0006752321750917526</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0.00014734774066799128 +/- 0.0009069835615235408</t>
+          <t>-0.00279960707269149 +/- 0.0005402750491158944</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>-0.005402750491159114 +/- 0.0008507125773913767</t>
+          <t>-0.0008349705304518285 +/- 0.0006963382553417374</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>0.0004911591355599709 +/- 0.0</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.000687622789783926 +/- 0.0008840864440078502</t>
+          <t>-0.00044204322200388504 +/- 0.0006752321750917139</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>4.91159135560193e-05 +/- 0.00034381139489194474</t>
+          <t>0.0007858546168959424 +/- 0.0003929273084479573</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>0.00014734774066799128 +/- 0.00022507739169726432</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.000785854616895909 +/- 0.0013397035065801372</t>
+          <t>0.0006876227897839482 +/- 0.000937071907089347</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1281,37 +1281,37 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.00029469548133598256 +/- 0.00024061785292568027</t>
+          <t>0.00024557956777998546 +/- 0.0003294795644646388</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>-0.0029469548133594925 +/- 0.0014897594192635696</t>
+          <t>-0.002406679764243558 +/- 0.000890881981690431</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>4.91159135560304e-05 +/- 0.0008055608775469748</t>
+          <t>-0.0017190569744596762 +/- 0.0007995491451915227</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.0009332023575638893 +/- 0.0007750360431267058</t>
+          <t>0.000589390962671954 +/- 0.0004281826074205186</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>-0.004371316306483264 +/- 0.0008349705304518834</t>
+          <t>-0.0024066797642435466 +/- 0.0005995361304387855</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.0022102161100196805 +/- 0.0011879554638946903</t>
+          <t>0.001571709233791818 +/- 0.0009523928992959295</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.0011296660117878442 +/- 0.0008799839325721578</t>
+          <t>0.0011296660117878887 +/- 0.0005832191594812476</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.0005756148613291212 +/- 0.0009198532617083606</t>
+          <t>-0.003976975405546856 +/- 0.0013071686024905078</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1331,157 +1331,157 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.0009942438513867225 +/- 0.0014511171767516392</t>
+          <t>0.0005756148613291212 +/- 0.0008895866038723127</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.007692307692307676 +/- 0.0016720612567943964</t>
+          <t>-0.0029827315541601563 +/- 0.000239799879380196</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.0005232862375719293 +/- 0.0011223239450302055</t>
+          <t>-0.00026164311878600354 +/- 0.0007492318714430311</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.0008372579801151136 +/- 0.0011271930522520973</t>
+          <t>5.232862375714742e-05 +/- 0.0007193996381406316</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.009209837781266317 +/- 0.0010775123119818898</t>
+          <t>-0.0008372579801151581 +/- 0.0019183990350416927</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.00015698587127157548 +/- 0.0004086996167402487</t>
+          <t>5.232862375719183e-05 +/- 0.00015698587127157548</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.0023024594453165737 +/- 0.0009419152276295158</t>
+          <t>-0.006122448979591877 +/- 0.000966310063454712</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.020355834641548932 +/- 0.002019234053539992</t>
+          <t>0.007273678702250097 +/- 0.0025896060767469638</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.012140240711669303 +/- 0.0021035846407369725</t>
+          <t>0.01894296180010463 +/- 0.00298594298643372</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.004133961276818443 +/- 0.001133250017148506</t>
+          <t>0.005442176870748261 +/- 0.0015906524493533127</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>-0.0014652014652014266 +/- 0.0014763721590440404</t>
+          <t>-0.003924646781789676 +/- 0.0005850517994505065</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.002564102564102577 +/- 0.0008257317550004905</t>
+          <t>0.0018838304552589945 +/- 0.000998366511163727</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.01883830455259029 +/- 0.0030602180046495992</t>
+          <t>0.02260596546310828 +/- 0.0024521977004416384</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.03401360544217689 +/- 0.0019994739062839024</t>
+          <t>0.04071166928309783 +/- 0.003111683672908128</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.004186289900575635 +/- 0.001281784271472115</t>
+          <t>-0.0014652014652015155 +/- 0.0006942176431931702</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.0016745159602302717 +/- 0.0009873344983837358</t>
+          <t>-0.0007326007326007855 +/- 0.000881857642404661</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.0002616431187859924 +/- 0.002479405073884281</t>
+          <t>-0.0008895866038723721 +/- 0.0008123586968215728</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0.002302459445316607 +/- 0.0008173992334805472</t>
+          <t>0.00251177394034533 +/- 0.0009002956846721631</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-5.232862375719183e-05 +/- 0.00015698587127157548</t>
+          <t>-0.00010465724751440586 +/- 0.00020931449502881172</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.007430664573521717 +/- 0.001188677832715902</t>
+          <t>0.0029827315541600895 +/- 0.0014244539601063475</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.004552590266876 +/- 0.0008771875779298966</t>
+          <t>0.002721088435374097 +/- 0.000610251375703306</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.001465201465201471 +/- 0.0007690705628832605</t>
+          <t>-0.000523286237571996 +/- 0.00066191055157894</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>-0.003244374672946071 +/- 0.0013605442176870847</t>
+          <t>-0.0006802721088435715 +/- 0.0008771875779298999</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.0013605442176870875 +/- 0.0010517923203684722</t>
+          <t>0.001465201465201449 +/- 0.000456190365624365</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>5.232862375720293e-05 +/- 0.0006387522561869923</t>
+          <t>5.232862375719183e-05 +/- 0.00015698587127157548</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>-0.00031397174254315096 +/- 0.0013071686024905033</t>
+          <t>-0.0018838304552590834 +/- 0.0006701333581824056</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.004761904761904778 +/- 0.001710913942885603</t>
+          <t>0.00423861852433276 +/- 0.0016622061930160726</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0.008110936682365278 +/- 0.0013894210410624512</t>
+          <t>0.006541077969649356 +/- 0.0011038735274583591</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0036106750392464913 +/- 0.0012260988502208424</t>
+          <t>-0.0016745159602302828 +/- 0.0009873344983837168</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>-5.232862375719183e-05 +/- 0.0004936672491918367</t>
+          <t>-5.232862375720293e-05 +/- 0.00036630036630037297</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.0025117739403453855 +/- 0.0005127137085888536</t>
+          <t>-0.0001569858712716199 +/- 0.00047095761381477335</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1491,122 +1491,122 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.003872318158032473 +/- 0.0015381411257665164</t>
+          <t>0.005023547880690704 +/- 0.0009705513862371283</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.0076399790685505176 +/- 0.001465201465201468</t>
+          <t>0.002564102564102533 +/- 0.0014698662381149375</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.00041862899005753464 +/- 0.00020931449502876732</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-0.000994243851386667 +/- 0.0006387522561870041</t>
+          <t>5.2328623757169625e-05 +/- 0.0003663003663003777</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-0.0013605442176870541 +/- 0.0009705513862371283</t>
+          <t>-0.0035583464154892884 +/- 0.0009591995175208471</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>0.00795395081109369 +/- 0.001014689661416285</t>
+          <t>0.002825745682888503 +/- 0.0007474022426523023</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>0.0017791732077446442 +/- 0.0006279434850863537</t>
+          <t>-0.0007326007326007745 +/- 0.00047959975876042595</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.0020408163265305925 +/- 0.001248232385335052</t>
+          <t>-0.00047095761381480414 +/- 0.0005463268712145804</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.005651491365777106 +/- 0.0012338907506594804</t>
+          <t>0.0003139717425431288 +/- 0.0006701333581823952</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.0029304029304029534 +/- 0.0007474022426523162</t>
+          <t>0.0017791732077446 +/- 0.0009983665111637327</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-0.0023024594453165625 +/- 0.0014080192618601464</t>
+          <t>0.0015175300889586295 +/- 0.0012482323853350733</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>-0.005808477237048637 +/- 0.0010838469480485649</t>
+          <t>-0.002668759811617005 +/- 0.0008582532426403166</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-0.006645735217163773 +/- 0.0010478798741235364</t>
+          <t>-0.004238618524332849 +/- 0.0015066645786382048</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-0.024123495552066953 +/- 0.0024594453165881773</t>
+          <t>-0.009471480900052376 +/- 0.0021884378510022492</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-0.0008372579801150914 +/- 0.000627943485086337</t>
+          <t>0.0013082155939298512 +/- 0.0005362088312904172</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>-0.014965986394557807 +/- 0.0017543751558597783</t>
+          <t>-0.005180533751962357 +/- 0.0007565061378755003</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>-0.00392464678178962 +/- 0.0018758187680727304</t>
+          <t>-0.008163265306122491 +/- 0.0015021140862801915</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0.005546834118262722 +/- 0.0018157353817789233</t>
+          <t>0.00015698587127154217 +/- 0.0011476563160367206</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-0.003610675039246469 +/- 0.00137356407623304</t>
+          <t>0.0008895866038722833 +/- 0.001424453960106325</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-0.00047095761381472646 +/- 0.00015698587127157548</t>
+          <t>-0.0010989010989011394 +/- 0.0006802721088435365</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>5.232862375719183e-05 +/- 0.00028179826306301195</t>
+          <t>-0.00020931449502883392 +/- 0.00041862899005758457</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0.00010465724751438366 +/- 0.00020931449502876732</t>
+          <t>-0.002616431187859802 +/- 0.0005732313527003143</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>0.0010989010989011284 +/- 0.0011332500171484933</t>
+          <t>0.0037676609105180116 +/- 0.001340266716364793</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-0.007849293563579274 +/- 0.0017822487039169503</t>
+          <t>-0.002145473574045054 +/- 0.0007193996381406308</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1616,92 +1616,92 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>0.00010465724751439476 +/- 0.00045619036562434464</t>
+          <t>-0.0003139717425432176 +/- 0.0002563568542944574</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>-0.008948194662480346 +/- 0.001849356048882505</t>
+          <t>-0.0026687598116169942 +/- 0.0007565061378754834</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>-0.0035583464154892554 +/- 0.0019551587328382383</t>
+          <t>0.004604918890633136 +/- 0.0010413264647897624</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>-0.00041862899005753464 +/- 0.00020931449502876732</t>
+          <t>-0.000156985871271631 +/- 0.0004086996167402985</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-0.02543171114599685 +/- 0.0015021140862802034</t>
+          <t>-0.0058084772370486926 +/- 0.0013123952071150806</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-0.005546834118262678 +/- 0.0013071686024904961</t>
+          <t>-0.0018315018315018694 +/- 0.0010267617409915554</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-0.004814233385661948 +/- 0.0020104000745472224</t>
+          <t>-0.0015175300889587074 +/- 0.0005943389163579604</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-0.0014652014652014379 +/- 0.0009873344983837393</t>
+          <t>-0.0004709576138147931 +/- 0.0004936672491918791</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>-0.002354788069073832 +/- 0.0006301200721502997</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>-0.0017268445839874857 +/- 0.0007418862835561372</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>-0.00010465724751443917 +/- 0.0008372579801151179</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>0.0014652014652014155 +/- 0.0010413264647897468</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>-0.0010465724751439365 +/- 0.0013029722237560036</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>-0.0014652014652015044 +/- 0.0009002956846721773</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
           <t>5.232862375719183e-05 +/- 0.00015698587127157548</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>-0.004081632653061207 +/- 0.0013196776779611284</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>-0.00659340659340657 +/- 0.000850239498130388</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>-0.0019361590790161864 +/- 0.0010736935912445344</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>-0.00293040293040292 +/- 0.0008818576424046345</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>0.0010989010989011171 +/- 0.0011088236577926193</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>-0.002145473574044987 +/- 0.0012913618711934156</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>-0.0005232862375719293 +/- 0.0005232862375719405</t>
+          <t>0.0011512297226582645 +/- 0.0006942176431931753</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>-0.0005756148613291101 +/- 0.0003663003663003428</t>
+          <t>0.0003139717425431288 +/- 0.0005336493473147871</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>-0.0008372579801151026 +/- 0.00062794348508635</t>
+          <t>-0.00010465724751441696 +/- 0.00031397174254319535</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>-0.001046572475143881 +/- 0.0009360828791207744</t>
+          <t>-0.00010465724751443917 +/- 0.0006102513757033366</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1726,37 +1726,37 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.0002093144950287784 +/- 0.0003471088215965927</t>
+          <t>-0.0003663003663003872 +/- 0.0004709576138147783</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.0020931449502878175 +/- 0.00066191055157894</t>
+          <t>-0.00031397174254319535 +/- 0.00041862899005758457</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>-0.005756148613291445 +/- 0.0008437737046884939</t>
+          <t>0.00047095761381470423 +/- 0.0011571608784665662</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>5.232862375720293e-05 +/- 0.0005943389163579368</t>
+          <t>0.00041862899005753464 +/- 0.00020931449502876732</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>-5.2328623757180724e-05 +/- 0.0007918757692528005</t>
+          <t>-0.0007849293563579884 +/- 0.0011284070461982062</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>-0.0029304029304029087 +/- 0.0017228757334541293</t>
+          <t>-0.0008372579801151803 +/- 0.0011271930522521148</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>-0.0006279434850863241 +/- 0.001141675783844665</t>
+          <t>-0.0006279434850863796 +/- 0.0006102513757033327</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-0.002108433734939763 +/- 0.0014570345328250415</t>
+          <t>-0.01012048192771089 +/- 0.0019201659578926894</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1776,157 +1776,157 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.010602409638554211 +/- 0.001455788671517408</t>
+          <t>-0.0060843373493976284 +/- 0.0019135397800323732</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.006927710843373491 +/- 0.0013802938840228507</t>
+          <t>-0.012469879518072314 +/- 0.001452044673878775</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.0017469879518072107 +/- 0.0008708935117350042</t>
+          <t>-0.0008433734939759408 +/- 0.0015523010514126516</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.0025903614457831294 +/- 0.001112420801965026</t>
+          <t>-0.009397590361445819 +/- 0.0012404373663839861</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.006987951807228931 +/- 0.0015287442819818592</t>
+          <t>0.00463855421686743 +/- 0.0022548153340015515</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.000120481927710836 +/- 0.00024096385542167202</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.002469879518072282 +/- 0.001836114536641955</t>
+          <t>-0.010120481927710877 +/- 0.002266853942436963</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-0.0069277108433734805 +/- 0.0022092916651677338</t>
+          <t>-0.0031325301204819687 +/- 0.002151876036083326</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.007469879518072287 +/- 0.0050199196761445105</t>
+          <t>0.00048192771084333287 +/- 0.002234606866384501</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-0.002048192771084323 +/- 0.001149324339056572</t>
+          <t>0.013253012048192746 +/- 0.0021720188406409474</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.0006626506024096313 +/- 0.0012182980973588261</t>
+          <t>-0.01548192771084339 +/- 0.0018868023811284178</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-0.00698795180722891 +/- 0.0010151987678525718</t>
+          <t>-0.003795180722891589 +/- 0.001980636412382348</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.013012048192771075 +/- 0.0025586458532042542</t>
+          <t>0.014036144578313226 +/- 0.001767638644713402</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.0032530120481927827 +/- 0.002776317740193453</t>
+          <t>0.006265060240963838 +/- 0.0016867469879518022</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.0009036144578313254 +/- 0.0012123260118974875</t>
+          <t>0.0016867469879517706 +/- 0.001957599615574931</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-0.00186746987951808 +/- 0.0017758316834920016</t>
+          <t>-0.016204819277108474 +/- 0.0017344795239624088</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.009036144578313254 +/- 0.0014755962305922673</t>
+          <t>-0.004156626506024141 +/- 0.002308887698402021</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-0.010783132530120499 +/- 0.0021118732702359202</t>
+          <t>-0.008072289156626533 +/- 0.0012976300740083183</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-1.1102230246251566e-17 +/- 0.00026940578042166974</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.004939759036144575 +/- 0.0013416299669469789</t>
+          <t>0.01746987951807224 +/- 0.0018858404629516312</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.001626506024096397 +/- 0.0012360412366676675</t>
+          <t>-0.003975903614457865 +/- 0.0019087927129824943</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-0.0013855421686746916 +/- 0.000764372140990931</t>
+          <t>0.005301204819277072 +/- 0.0008853577383553808</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.0003614457831325302 +/- 0.0006143397004328585</t>
+          <t>0.007951807228915619 +/- 0.0010007980557732476</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.0033132530120481896 +/- 0.0006172861907204523</t>
+          <t>0.00945783132530117 +/- 0.001943646482518268</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.00048192771084336615 +/- 0.0007991866964711685</t>
+          <t>-0.0003012048192771455 +/- 0.0003012048192771455</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.00289156626506023 +/- 0.001228679400865743</t>
+          <t>0.0015662650602409234 +/- 0.0008604130636798788</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.007048192771084339 +/- 0.0018674698795180607</t>
+          <t>0.010240963855421637 +/- 0.0020517332970995776</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-0.0016265060240963857 +/- 0.0012360412366676605</t>
+          <t>-0.0001807228915662984 +/- 0.0007153218124721647</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-0.007289156626506033 +/- 0.0015346673738381982</t>
+          <t>0.004638554216867441 +/- 0.0014268336484731443</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.0003614457831325302 +/- 0.0009016041895840848</t>
+          <t>0.000843373493975863 +/- 0.0006143397004328563</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.000120481927710836 +/- 0.00036144578313250796</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1936,122 +1936,122 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.005421686746987964 +/- 0.0021720188406409565</t>
+          <t>0.005662650602409602 +/- 0.0012693558738376795</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.001566265060240979 +/- 0.0012404373663839807</t>
+          <t>-0.0059638554216867815 +/- 0.0016705330872122909</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>-0.0006024096385542244 +/- 0.0007127806967589932</t>
+          <t>6.0240963855384686e-05 +/- 0.0005003990278866445</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>1.1102230246251566e-17 +/- 0.0006024096385542022</t>
+          <t>0.000120481927710836 +/- 0.00024096385542167202</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-0.0007831325301204783 +/- 0.0005421686746988089</t>
+          <t>0.014457831325301184 +/- 0.001347028902108304</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.004277108433734933 +/- 0.0016040393922523274</t>
+          <t>0.006867469879518018 +/- 0.0021247219383793326</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.0005421686746987953 +/- 0.0005003990278866444</t>
+          <t>-0.00036144578313255236 +/- 0.0010503370948290811</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.009397590361445796 +/- 0.0015048187947947968</t>
+          <t>0.0072289156626505705 +/- 0.0020339690380884435</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.0019879518072289048 +/- 0.0010098225671229086</t>
+          <t>0.004698795180722859 +/- 0.0019575996155749183</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>-0.0038554216867469626 +/- 0.00166509336880544</t>
+          <t>-0.00753012048192776 +/- 0.0020384246163480343</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-0.0010843373493976017 +/- 0.0015192193027612653</t>
+          <t>0.008674698795180702 +/- 0.0018703824935252988</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>-0.005722891566265054 +/- 0.0015534695130394662</t>
+          <t>-0.010783132530120521 +/- 0.001436971137575496</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.002108433734939763 +/- 0.001016984519044202</t>
+          <t>0.0005421686746987509 +/- 0.0005683121163889396</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.0007831325301204783 +/- 0.0008540630649854042</t>
+          <t>-0.0001204819277108804 +/- 0.0008853577383553581</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.0003012048192771011 +/- 0.0004041086706324922</t>
+          <t>0.001144578313252953 +/- 0.00032440751850208136</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.001807228915662662 +/- 0.0006599066957893366</t>
+          <t>0.0031927710843373093 +/- 0.0017049363491668725</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>-0.0016867469879518037 +/- 0.0006488150370041359</t>
+          <t>-0.004096385542168712 +/- 0.0019389731252326629</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-0.003554216867469884 +/- 0.0017961507850452478</t>
+          <t>0.0016265060240963415 +/- 0.002222393583818867</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-0.0043975903614457915 +/- 0.002318298964445032</t>
+          <t>0.0038554216867469626 +/- 0.0020196451342458085</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.000120481927710836 +/- 0.00036144578313250796</t>
+          <t>0.00036144578313249685 +/- 0.0004819277108433661</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>-0.00030120481927709 +/- 0.0007253972637826701</t>
+          <t>-6.02409638554513e-05 +/- 0.00042168674698796877</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.0010843373493976017 +/- 0.0005251685474145501</t>
+          <t>-0.001325301204819307 +/- 0.0018430191012986001</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.0014457831325301207 +/- 0.002055267724003844</t>
+          <t>0.0037951807228915222 +/- 0.0018281916753606477</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-0.002168674698795192 +/- 0.002107572974040478</t>
+          <t>-0.00030120481927713437 +/- 0.0017717398999822476</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2061,42 +2061,42 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>-0.00036144578313251907 +/- 0.0003995933482355893</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.0005421686746987953 +/- 0.0013321291799696527</t>
+          <t>0.0007228915662650271 +/- 0.001368411649590416</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.0012650602409638556 +/- 0.002355568047712911</t>
+          <t>0.006265060240963838 +/- 0.0009787998077874721</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>-0.0011445783132530197 +/- 0.0008281763304137013</t>
+          <t>0.0010240963855421281 +/- 0.0008104592799442125</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.0010843373493975906 +/- 0.0007524093973973975</t>
+          <t>-0.0016867469879518371 +/- 0.001611938332561398</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-0.001867469879518102 +/- 0.0021459654374164894</t>
+          <t>0.0036144578313252683 +/- 0.001292024734308872</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-0.004638554216867474 +/- 0.0029640758072632667</t>
+          <t>-0.0029518072289156927 +/- 0.0015812535841453882</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.0007831325301204672 +/- 0.0008104592799441918</t>
+          <t>0.0019879518072288827 +/- 0.0010451416610179174</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2106,47 +2106,47 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.0005421686746987953 +/- 0.0005003990278866445</t>
+          <t>-0.0026506024096386027 +/- 0.0007714607514979419</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>-0.0003614457831325413 +/- 0.0006708149834734973</t>
+          <t>0.002469879518072271 +/- 0.0010589395079064396</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.00024096385542168308 +/- 0.0005521175536091229</t>
+          <t>-0.0011445783132530529 +/- 0.00042168674698792594</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.0001807228915662651 +/- 0.0012063243611145017</t>
+          <t>0.0013855421686746693 +/- 0.0007643721409909363</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.0013855421686747138 +/- 0.00047049696842810137</t>
+          <t>0.0012650602409638224 +/- 0.001558134597153925</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.0033132530120481896 +/- 0.001431911364337909</t>
+          <t>0.004638554216867441 +/- 0.0014520446738787687</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>-0.000240963855421672 +/- 0.0002951192461184371</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>-0.0008433734939759074 +/- 0.0010843373493975917</t>
+          <t>-0.0007831325301205338 +/- 0.00038573037574896567</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>-0.0013253012048192847 +/- 0.0005251685474145373</t>
+          <t>-0.0005421686746988286 +/- 0.0005003990278866485</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.000120481927710836 +/- 0.00036144578313250796</t>
+          <t>-0.00048192771084341055 +/- 0.00045080209479206096</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.002048192771084334 +/- 0.0005521175536091229</t>
+          <t>0.006204819277108397 +/- 0.0011758567045748879</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2171,37 +2171,37 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.00036144578313251907 +/- 0.0005521175536091205</t>
+          <t>-0.00048192771084341055 +/- 0.0006488150370041607</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>-0.0005421686746987841 +/- 0.0007831325301204697</t>
+          <t>-0.0037951807228916003 +/- 0.0012360412366676555</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>-0.0011445783132530197 +/- 0.0010926721173022307</t>
+          <t>0.0038554216867469405 +/- 0.001117303433192252</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>-0.000240963855421672 +/- 0.0002951192461184371</t>
+          <t>0.0003614457831324858 +/- 0.000940993936856224</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>-0.0030722891566264954 +/- 0.0008281763304136988</t>
+          <t>0.005662650602409602 +/- 0.0013789786918385124</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.0028313253012048232 +/- 0.0012650602409638614</t>
+          <t>0.0008433734939758741 +/- 0.0008171481907379684</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>-0.0002409638554216942 +/- 0.0010151987678525716</t>
+          <t>-0.003975903614457854 +/- 0.0006143397004328781</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.0036732456140351035 +/- 0.0016272831227692683</t>
+          <t>-0.0015350877192982892 +/- 0.0006393587603997222</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2221,92 +2221,92 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.0016995614035087536 +/- 0.0011355435952416582</t>
+          <t>-0.0017543859649123195 +/- 0.0008771929824561388</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0011513157894736947 +/- 0.002072484448622368</t>
+          <t>0.00723684210526313 +/- 0.0019274556832507602</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.0042214912280701955 +/- 0.001251393882731742</t>
+          <t>0.00405701754385962 +/- 0.001592745509466442</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.0026864035087719174 +/- 0.001418039161883516</t>
+          <t>0.004605263157894712 +/- 0.0013020111937541458</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.008662280701754366 +/- 0.0016773090505239436</t>
+          <t>0.007839912280701722 +/- 0.0020076571736404075</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.00010964912280702066 +/- 0.00021929824561404133</t>
+          <t>0.0005482456140350922 +/- 0.00024518289226969594</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.0012061403508771829 +/- 0.0010909949968274195</t>
+          <t>-0.0011513157894737168 +/- 0.0008651169867357428</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-0.023190789473684203 +/- 0.0032066510561161716</t>
+          <t>-0.04671052631578952 +/- 0.0030994065844523098</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.020285087719298232 +/- 0.0025243123757064355</t>
+          <t>-0.041392543859649175 +/- 0.002597666171158384</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.004331140350877205 +/- 0.001212354407209204</t>
+          <t>-0.001535087719298267 +/- 0.001847839862538667</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.0002192982456140524 +/- 0.001206140350877205</t>
+          <t>-0.007236842105263197 +/- 0.0016773090505239501</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.00570175438596493 +/- 0.0018864748392637429</t>
+          <t>0.004660087719298189 +/- 0.0015163724436336996</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.030537280701754398 +/- 0.002901561101403345</t>
+          <t>0.02538377192982453 +/- 0.002500985685955503</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.012609649122807032 +/- 0.0018672572769655954</t>
+          <t>0.00992324561403506 +/- 0.0017241431133241784</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>-0.002576754385964897 +/- 0.0010416666666666588</t>
+          <t>-0.004331140350877227 +/- 0.0013305549451218877</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.003234649122807032 +/- 0.0013966819301378303</t>
+          <t>0.0030153508771929237 +/- 0.0015360664173379296</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>-0.01255482456140351 +/- 0.0013077697852934911</t>
+          <t>-0.004989035087719351 +/- 0.001758663918020348</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.0017543859649122417 +/- 0.0009108140200568029</t>
+          <t>-0.004166666666666707 +/- 0.0017543859649122898</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -2316,62 +2316,62 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.005756578947368407 +/- 0.0020840545842925797</t>
+          <t>-0.007949561403508809 +/- 0.0017891632535176278</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.006304824561403533 +/- 0.0009574698024436769</t>
+          <t>0.004769736842105243 +/- 0.0015516416335619378</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-0.008442982456140335 +/- 0.001206140350877188</t>
+          <t>-0.005263157894736881 +/- 0.001648387760786513</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.0016447368421052878 +/- 0.0008131796586727633</t>
+          <t>-0.0028508771929824815 +/- 0.0008422308934066263</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.006633771929824539 +/- 0.000865116986735714</t>
+          <t>-0.004989035087719318 +/- 0.0011087581368507</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.0005482456140351033 +/- 0.0004246692265578428</t>
+          <t>-0.0001644736842105421 +/- 0.0005509800230877583</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>-0.010197368421052622 +/- 0.0018050523720563834</t>
+          <t>-0.008662280701754422 +/- 0.001958395953891646</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.004057017543859664 +/- 0.0010168441332780464</t>
+          <t>0.00740131578947365 +/- 0.0013706140350877006</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-0.002850877192982426 +/- 0.0006393587603997222</t>
+          <t>0.0018640350877192735 +/- 0.0013473909788864558</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0002192982456140524 +/- 0.0017543859649122805</t>
+          <t>0.003015350877192946 +/- 0.002182678644451149</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>-0.0024122807017543544 +/- 0.0006105004783804783</t>
+          <t>-0.000328947368421062 +/- 0.00026858440162097014</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.0008771929824561653 +/- 0.0003636649989424884</t>
+          <t>-0.000822368421052655 +/- 0.0003677743384045812</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -2381,107 +2381,107 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.006469298245614053 +/- 0.0010049508102973194</t>
+          <t>0.004550438596491191 +/- 0.0014095351022129772</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.0030153508771929793 +/- 0.0014761964931838095</t>
+          <t>0.005153508771929794 +/- 0.00110196004617552</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.000493421052631593 +/- 0.00045540701002841615</t>
+          <t>-0.000328947368421062 +/- 0.00055910301684133</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>5.482456140351033e-05 +/- 0.0003837719298245723</t>
+          <t>0.00021929824561400801 +/- 0.0007830513627788062</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.0020833333333333593 +/- 0.0008771929824561264</t>
+          <t>-0.005043859649122839 +/- 0.0010049508102973619</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.0033442982456140524 +/- 0.0011617116283123405</t>
+          <t>0.005263157894736792 +/- 0.0011552251921987653</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.0003837719298245723 +/- 0.000493421052631593</t>
+          <t>-0.000657894736842124 +/- 0.0005904785972735369</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.001699561403508809 +/- 0.000753713107722998</t>
+          <t>-0.0032346491228070428 +/- 0.0008991896637530908</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.0009320175438596757 +/- 0.0010701327464881407</t>
+          <t>-0.0002741228070175739 +/- 0.0019956441582457546</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.00241228070175441 +/- 0.0009239199312693217</t>
+          <t>-0.005537280701754399 +/- 0.001724143113324166</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-0.01589912280701753 +/- 0.0011500097019409513</t>
+          <t>-0.03887061403508775 +/- 0.0028429588075579476</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>-0.014473684210526305 +/- 0.0013912913969791195</t>
+          <t>-0.01885964912280704 +/- 0.0023796638612073114</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-0.0008223684210526327 +/- 0.0007849682600480292</t>
+          <t>-0.006853070175438636 +/- 0.0013923711731579184</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.0030701754385964895 +/- 0.0006578947368420943</t>
+          <t>-0.005921052631578982 +/- 0.0012210009567609724</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-0.000328947368421062 +/- 0.0003636649989424884</t>
+          <t>-0.003289473684210542 +/- 0.0006005729797205533</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>-0.0038925438596491223 +/- 0.001500431160460968</t>
+          <t>0.003344298245614008 +/- 0.0015974563908260609</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>-0.004714912280701755 +/- 0.001278717520799412</t>
+          <t>-0.02132675438596495 +/- 0.0029057017543859614</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-0.008607456140350878 +/- 0.0015124028754532432</t>
+          <t>-0.030701754385964942 +/- 0.003081901167227033</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-0.009484649122807009 +/- 0.001532147874175665</t>
+          <t>-0.03426535087719301 +/- 0.00230328415982456</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-0.0023026315789473452 +/- 0.0011182060336826305</t>
+          <t>0.001096491228070129 +/- 0.0007753363828799612</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.00010964912280702066 +/- 0.00041026945030417193</t>
+          <t>-1.1102230246251566e-17 +/- 0.0004903657845394167</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-0.020888157894736838 +/- 0.002553318206621702</t>
+          <t>-0.03925438596491233 +/- 0.0022093686052203996</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-0.010307017543859643 +/- 0.0012210009567609624</t>
+          <t>-0.01990131578947373 +/- 0.0021381578947368206</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2506,92 +2506,92 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>-0.002686403508771906 +/- 0.0006692190578801299</t>
+          <t>-0.00202850877192986 +/- 0.0009190271170087792</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.0030153508771929905 +/- 0.0014137935261214454</t>
+          <t>-0.0012609649122807265 +/- 0.0009511705906193823</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>-0.01661184210526314 +/- 0.0016638147922690301</t>
+          <t>-0.03015350877192984 +/- 0.0026746295872040553</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.0012609649122807375 +/- 0.00035104847792944246</t>
+          <t>-0.0007127192982456342 +/- 0.0005509800230877838</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-0.0035635964912280717 +/- 0.0011302372877241473</t>
+          <t>0.008004385964912254 +/- 0.0009558988911273283</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-0.008004385964912287 +/- 0.000986842105263186</t>
+          <t>-0.02669956140350881 +/- 0.0020955608392123353</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-0.010855263157894734 +/- 0.0017127740517339266</t>
+          <t>-0.021710526315789503 +/- 0.002538560724296109</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.0014802631578947566 +/- 0.0007772723069494283</t>
+          <t>-0.0009320175438596867 +/- 0.001097860986540624</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.000164473684210531 +/- 0.00025123770257434047</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.001535087719298267 +/- 0.0009432374196318589</t>
+          <t>0.003344298245614019 +/- 0.0006692190578801563</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.005701754385964941 +/- 0.0008563870258669451</t>
+          <t>0.005153508771929794 +/- 0.0013912913969791072</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.0014254385964912685 +/- 0.00055910301684133</t>
+          <t>-0.004769736842105299 +/- 0.001492396665440396</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.00350877192982455 +/- 0.000702096955858885</t>
+          <t>0.000383771929824539 +/- 0.0009511705906193618</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.0019736842105263276 +/- 0.000986842105263139</t>
+          <t>-0.00010964912280704286 +/- 0.0018315014351414454</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.011458333333333338 +/- 0.0009320175438596567</t>
+          <t>0.003563596491228049 +/- 0.0009883638364758809</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>5.482456140351033e-05 +/- 0.0003837719298245723</t>
+          <t>0.000164473684210531 +/- 0.00025123770257434047</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.003673245614035081 +/- 0.00042819351293349104</t>
+          <t>0.00021929824561404133 +/- 0.00026858440162097014</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>-0.0008223684210526217 +/- 0.0011822290928096295</t>
+          <t>0.0002192982456140302 +/- 0.0004385964912280604</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.0021381578947368696 +/- 0.0007537131077229786</t>
+          <t>0.00148026315789469 +/- 0.0008150256988661364</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>-0.0015899122807017441 +/- 0.0009637278416253608</t>
+          <t>0.00043859649122802714 +/- 0.0012453746372368985</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2616,37 +2616,37 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>-0.0004934210526315819 +/- 0.0004554070100283881</t>
+          <t>-0.001315789473684248 +/- 0.0006105004783805022</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>-0.000328947368421062 +/- 0.0008907936847188806</t>
+          <t>0.0013706140350876693 +/- 0.0008924791993475629</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.004714912280701778 +/- 0.0014127301235444232</t>
+          <t>0.0004934210526315597 +/- 0.000963727841625362</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>-0.0005482456140351033 +/- 0.0005482456140351033</t>
+          <t>-0.0010964912280702066 +/- 0.0006486929586732219</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>-0.0007675438596491113 +/- 0.0007830513627787984</t>
+          <t>-0.004440789473684248 +/- 0.0016346547714776007</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.004440789473684215 +/- 0.0012123544072092244</t>
+          <t>0.0012609649122806489 +/- 0.0008511060688738961</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>-0.0022478070175438345 +/- 0.0011355435952416647</t>
+          <t>0.0015899122807017108 +/- 0.0009320175438596377</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.006467661691542259 +/- 0.0013775495626729747</t>
+          <t>0.0034273079049198297 +/- 0.000595374771380263</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2666,157 +2666,157 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.010392482034273143 +/- 0.001043005100282649</t>
+          <t>-0.015146489773355375 +/- 0.0009950248756218861</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0013266998341625146 +/- 0.0006155626714018791</t>
+          <t>-0.003372028745163058 +/- 0.0010026731424663887</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.0015478164731896004 +/- 0.0012060488794511516</t>
+          <t>-0.0012714206744057432 +/- 0.0010503040353786576</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.00840243228302926 +/- 0.000982663838288065</t>
+          <t>0.00016583747927031433 +/- 0.0004975124378109431</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0003869541182974001 +/- 0.001106964311470464</t>
+          <t>-0.0012714206744057432 +/- 0.001106964311470464</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0006633499170812573 +/- 0.0006446602426584051</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.00033167495854062866 +/- 0.0010546591502674863</t>
+          <t>0.0017136539524599149 +/- 0.0012952321187241491</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.015146489773355388 +/- 0.0011382675667205174</t>
+          <t>0.0076285240464345596 +/- 0.0009826638382880826</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.016860143725815367 +/- 0.0020867425194225704</t>
+          <t>0.009563294637921571 +/- 0.0006080707573244859</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-0.00713101160862355 +/- 0.0013415877390284053</t>
+          <t>0.004588170259812041 +/- 0.0012123666224135839</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.0025428413488114863 +/- 0.0007498430053206453</t>
+          <t>-0.0014925373134328291 +/- 0.0010503040353786576</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-0.003372028745163058 +/- 0.0014297973638891658</t>
+          <t>-0.0014925373134328291 +/- 0.0014212227896276818</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.0016030956329463719 +/- 0.002866532263673657</t>
+          <t>-0.0017136539524599149 +/- 0.0017207719642093212</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.009673852957435003 +/- 0.0014255165238504775</t>
+          <t>0.0054726368159203845 +/- 0.0007599628018169024</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0.0027639579878385723 +/- 0.000699232207886869</t>
+          <t>0.0015478164731896004 +/- 0.001071902677151201</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-0.0018242122719734576 +/- 0.0011342335283959699</t>
+          <t>-0.0002211166390270858 +/- 0.0008981800336800358</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>0.008291873963515717 +/- 0.001159545437446265</t>
+          <t>0.004145936981757858 +/- 0.0008998795243836172</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.0013266998341625146 +/- 0.0013128073064718477</t>
+          <t>0.0014372581536760576 +/- 0.0007079186553270116</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.00027639579878385723 +/- 0.00044567483406846394</t>
+          <t>0.0002211166390270858 +/- 0.0005637390285895812</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.00497512437810943 +/- 0.0010488483118303033</t>
+          <t>0.005030403537866201 +/- 0.001032699927709747</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0.005196241017136516 +/- 0.0014874100660114593</t>
+          <t>-0.0006080707573244859 +/- 0.001492537313432829</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.002487562189054715 +/- 0.0010267648215039594</t>
+          <t>-0.0002211166390270858 +/- 0.0007079186553270115</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.0027639579878385723 +/- 0.0009888636716416936</t>
+          <t>0.0001105583195135429 +/- 0.0010132837357558471</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.008955223880596974 +/- 0.001043005100282649</t>
+          <t>0.0028192371475953435 +/- 0.000674768137962059</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.0007186290768380288 +/- 0.0006080707573244859</t>
+          <t>0.0003869541182974001 +/- 0.0004975124378109431</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>-0.002321724709784401 +/- 0.0014583643956078342</t>
+          <t>0.0009397457158651146 +/- 0.0006080707573244859</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-0.004311774461028173 +/- 0.0020801423684053836</t>
+          <t>-0.005251520176893287 +/- 0.0016258088634441875</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-0.0011608623548922004 +/- 0.001247154690180036</t>
+          <t>0.002708678828081801 +/- 0.0009066456311142428</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0061912658927584015 +/- 0.00137199266401225</t>
+          <t>-0.006467661691542259 +/- 0.001962994019299571</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0003869541182974001 +/- 0.0002533209339389618</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.001105583195135429 +/- 0.0</t>
+          <t>0.0005527915975677145 +/- 0.0</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -2826,122 +2826,122 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.0061912658927584015 +/- 0.0011542627428314542</t>
+          <t>-0.00016583747927031433 +/- 0.0008930621570703947</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>5.527915975677145e-05 +/- 0.0011179518195774789</t>
+          <t>-0.009784411276948545 +/- 0.0025578187509694246</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0.00016583747927031433 +/- 0.00025332093393896183</t>
+          <t>0.0007186290768380288 +/- 0.0005555486799956243</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-0.0006080707573244859 +/- 0.00045918318755765826</t>
+          <t>-5.527915975677145e-05 +/- 0.0007599628018168854</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.0029297954671088865 +/- 0.0009904075659020915</t>
+          <t>0.0030403537866224295 +/- 0.00044567483406846394</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>-0.0016583747927031434 +/- 0.0010775892034061824</t>
+          <t>-0.007683803206191231 +/- 0.002175640536667146</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>0.0008844665561083432 +/- 0.0004422332780541716</t>
+          <t>-0.0006633499170812573 +/- 0.00033167495854062866</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.000497512437810943 +/- 0.0005771313714157271</t>
+          <t>-0.0008844665561083432 +/- 0.0009950248756218861</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.0029850746268656582 +/- 0.0007498430053206453</t>
+          <t>0.001990049751243772 +/- 0.0017861243141407892</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.005583195135433916 +/- 0.0012714206744057432</t>
+          <t>0.0017136539524599149 +/- 0.0009066456311142428</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.013598673300165776 +/- 0.0012653978045615861</t>
+          <t>0.005085682697622973 +/- 0.0007739082365948002</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.007407407407407374 +/- 0.0007498430053206453</t>
+          <t>0.0036484245439469152 +/- 0.0007498430053206453</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.002321724709784401 +/- 0.0007333609265572989</t>
+          <t>-0.008070757324488632 +/- 0.0007079186553270116</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-0.010005527915975743 +/- 0.001247154690180036</t>
+          <t>0.0048645660585958875 +/- 0.000733360926557299</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>0.00033167495854062866 +/- 0.0003666804632786495</t>
+          <t>0.000497512437810943 +/- 0.0007186290768380288</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>0.002266445550027629 +/- 0.001247154690180036</t>
+          <t>-0.009894969596462088 +/- 0.0012714206744057432</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.00961857379767823 +/- 0.002086010200565298</t>
+          <t>0.000497512437810943 +/- 0.000971718951423265</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>0.005140961857379745 +/- 0.0011608623548922004</t>
+          <t>-0.001879491431730229 +/- 0.001698429131645898</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.004367053620784944 +/- 0.0017903963229078579</t>
+          <t>-0.005306799336650059 +/- 0.00196532767657613</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>0.0001105583195135429 +/- 0.0003316749585406286</t>
+          <t>-0.0004422332780541716 +/- 0.00022111663902708577</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>-0.0003869541182974001 +/- 0.0002533209339389618</t>
+          <t>-0.004477611940298487 +/- 0.001090275451814037</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.0008844665561083432 +/- 0.0003666804632786495</t>
+          <t>-0.001879491431730229 +/- 0.0003666804632786495</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.003980099502487544 +/- 0.0017269761582988654</t>
+          <t>0.004588170259812041 +/- 0.0013324456377218406</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-0.004311774461028173 +/- 0.0011542627428314542</t>
+          <t>-0.004532891100055258 +/- 0.0012798050749353424</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>0.002100608070757315 +/- 0.000733360926557299</t>
+          <t>0.0012714206744057432 +/- 0.0007014139049446911</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>0.0061912658927584015 +/- 0.0009183663751153164</t>
+          <t>0.0025428413488114863 +/- 0.0010546591502674863</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>0.011055831951354289 +/- 0.0016398448838243513</t>
+          <t>0.0020453289110005436 +/- 0.0016592958562524672</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
@@ -2971,22 +2971,22 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-0.003703703703703687 +/- 0.0011868938946149137</t>
+          <t>0.00033167495854062866 +/- 0.0009950248756218861</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-0.001879491431730229 +/- 0.0016803409788358865</t>
+          <t>-0.0017689331122166863 +/- 0.001071902677151201</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>0.017744610281923735 +/- 0.0011971480280656664</t>
+          <t>0.004090657822001098 +/- 0.0013128073064718692</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-0.000995024875621886 +/- 0.0005416229392555372</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2996,47 +2996,47 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.0015478164731896004 +/- 0.0011804398288591778</t>
+          <t>-0.003482587064676601 +/- 0.0010503040353786574</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>-0.006357103372028739 +/- 0.001644496935394548</t>
+          <t>-0.0016583747927031434 +/- 0.0006055528551743103</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.00033167495854062866 +/- 0.0004422332780541716</t>
+          <t>0.0030956329463792008 +/- 0.0011648041738919503</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0.010392482034273032 +/- 0.0008124344088833058</t>
+          <t>-0.004809286898839115 +/- 0.0010207952079944336</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>0.010447761194029802 +/- 0.0010326999277097467</t>
+          <t>-0.0017689331122166863 +/- 0.000690436484068366</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>0.005417357656163602 +/- 0.000982663838288065</t>
+          <t>0.0016030956329463719 +/- 0.001090275451814037</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-5.527915975677145e-05 +/- 0.0001658374792703143</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>-0.00027639579878385723 +/- 0.00027639579878385723</t>
+          <t>0.0011608623548922004 +/- 0.0007186290768380288</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>-0.00027639579878385723 +/- 0.00027639579878385723</t>
+          <t>0.0010503040353786574 +/- 0.0008365254809519894</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>0.000995024875621886 +/- 0.000733360926557299</t>
+          <t>0.005085682697622973 +/- 0.000595374771380263</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3061,37 +3061,37 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>0.0017136539524599149 +/- 0.0009397457158651146</t>
+          <t>0.0008844665561083432 +/- 0.00044223327805417153</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>-0.0013266998341625146 +/- 0.0007498430053206453</t>
+          <t>-0.004145936981757858 +/- 0.0007518778611794021</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>0.0017689331122166863 +/- 0.00041367135287716136</t>
+          <t>-0.0018242122719734576 +/- 0.00043174403957471635</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>0.002487562189054715 +/- 0.0011920319874432132</t>
+          <t>0.00016583747927031433 +/- 0.0002533209339389618</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>-0.007020453289110007 +/- 0.0016220454119537256</t>
+          <t>0.006025428413488132 +/- 0.0008722904277534683</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>0.0020453289110005436 +/- 0.00113423352839597</t>
+          <t>-0.004919845218352659 +/- 0.001295232118724149</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>-0.006025428413488099 +/- 0.0011179518195775014</t>
+          <t>-0.008955223880596974 +/- 0.0006446602426584051</t>
         </is>
       </c>
     </row>
@@ -3101,424 +3101,424 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>0.00012048192771082488 +/- 0.0003614457831325302</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.000240963855421672 +/- 0.0002951192461184371</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>-0.0001204819277108582 +/- 0.0002409638554217164</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.00030120481927707886 +/- 0.00040410867063249217</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.00042168674698792594 +/- 0.00027605877680455176</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-0.0002409638554217275 +/- 0.000552117553609152</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.000120481927710836 +/- 0.00024096385542167202</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0.00036144578313250796 +/- 0.0002951192461184371</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0.00060240963855418 +/- 0.0003809973084539983</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>-0.00030120481927713437 +/- 0.000404108670632517</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0.000843373493975863 +/- 0.0007714607514979436</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
           <t>0.000481927710843344 +/- 0.000240963855421672</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0.000481927710843344 +/- 0.000240963855421672</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0.00030120481927709 +/- 0.00030120481927709</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>-0.0001807228915663095 +/- 0.00047049696842813265</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>0.00060240963855418 +/- 0.0003809973084539983</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.00012048192771081378 +/- 0.00045080209479204903</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>-6.02409638554291e-05 +/- 0.0001807228915662873</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.0001807228915662429 +/- 0.0004704969684281014</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>0.000120481927710836 +/- 0.000240963855421672</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0.00018072289156625398 +/- 0.0002760587768045517</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>6.0240963855418e-05 +/- 0.00018072289156625398</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>0.000120481927710836 +/- 0.000240963855421672</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0.000120481927710836 +/- 0.000240963855421672</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>6.0240963855418e-05 +/- 0.00018072289156625398</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>-0.0002409638554217164 +/- 0.0002951192461184915</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-0.0007831325301205338 +/- 0.00038573037574896567</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>6.024096385540689e-05 +/- 0.00032440751850208136</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>-0.0003012048192771455 +/- 0.0003012048192771455</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-0.001325301204819318 +/- 0.0005251685474145297</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
         <is>
           <t>-0.0003614457831325746 +/- 0.0002951192461184915</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0.000481927710843344 +/- 0.000240963855421672</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>-0.0001204819277108582 +/- 0.0002409638554217164</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>0.00042168674698792594 +/- 0.00027605877680455176</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>-0.0010240963855422057 +/- 0.0005421686746987829</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0.000240963855421672 +/- 0.0002951192461184371</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
         <is>
           <t>6.0240963855418e-05 +/- 0.00018072289156625398</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>0.00018072289156625398 +/- 0.0002760587768045517</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>-0.0001807228915662873 +/- 0.0002760587768046026</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
         <is>
           <t>0.000120481927710836 +/- 0.00024096385542167202</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0.00042168674698792594 +/- 0.00027605877680455176</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0.000481927710843344 +/- 0.000240963855421672</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>6.024096385539579e-05 +/- 0.0009116112018326061</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0.010301204819277066 +/- 0.0019696123764182984</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>6.0240963855418e-05 +/- 0.00018072289156625398</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>0.00042168674698792594 +/- 0.0004704969684280829</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0.000240963855421672 +/- 0.0002951192461184371</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>0.000120481927710836 +/- 0.000240963855421672</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>0.000120481927710836 +/- 0.00024096385542167202</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>6.0240963855418e-05 +/- 0.00018072289156625398</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>-0.0001204819277108582 +/- 0.0002409638554217164</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="CH7" t="inlineStr">
         <is>
           <t>0.0 +/- 0.0</t>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.00060240963855418 +/- 0.0003809973084539983</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.016942811330839126 +/- 0.0015314322588877037</t>
+          <t>-0.014804917156600771 +/- 0.0016220193378400337</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3556,157 +3556,157 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.00598610368786745 +/- 0.0006232979043126991</t>
+          <t>-0.009727418492784634 +/- 0.001347890990156976</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.006894708711918785 +/- 0.0020762078674029954</t>
+          <t>-0.007856761090326037 +/- 0.0010702824369054524</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.0008551576696953722 +/- 0.0011005483849264768</t>
+          <t>-0.002137894174238397 +/- 0.001170972864789238</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.013415285943345834 +/- 0.0007347796410939325</t>
+          <t>-0.007215392838054513 +/- 0.000726962614042503</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.00026723677177979964 +/- 0.0012927190403471528</t>
+          <t>0.0012292891501870407 +/- 0.001219958547355763</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.00026723677177981076 +/- 0.00026723677177981076</t>
+          <t>-5.3447354355962154e-05 +/- 0.0005042213325524903</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.00678781400320686 +/- 0.0011475633647024983</t>
+          <t>-0.004436130411544637 +/- 0.0014351385977656472</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.01004810261892034 +/- 0.0017694222722871985</t>
+          <t>0.008925708177445212 +/- 0.002280768390523986</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.009246392303580953 +/- 0.0019129374845722512</t>
+          <t>0.009620523784072665 +/- 0.002402159813387932</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.0003206841261357285 +/- 0.0012465958086253935</t>
+          <t>0.00090860502405129 +/- 0.0010966480239809387</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.0003206841261357396 +/- 0.0017918818401112056</t>
+          <t>-0.00913949759486905 +/- 0.001538875472890212</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-0.004543025120256561 +/- 0.0011525311947005767</t>
+          <t>-0.00507749866381616 +/- 0.0010211102712209053</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>-0.004703367183324448 +/- 0.0014301537317220443</t>
+          <t>0.003901656867985015 +/- 0.0008297260660748277</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>-0.027204703367183326 +/- 0.00346749365757533</t>
+          <t>-0.020844468198824163 +/- 0.0030044830192528494</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0.00347407803313734 +/- 0.0008365834229021276</t>
+          <t>0.0002137894174238264 +/- 0.001246595808625386</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-0.007803313735970085 +/- 0.0007999267529179888</t>
+          <t>-0.0041688936397648365 +/- 0.001090116411243784</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.0014965259219668515 +/- 0.00121409050685203</t>
+          <t>0.0015499732763228137 +/- 0.0007726794385249152</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>-0.02244788882950296 +/- 0.0005344735435595772</t>
+          <t>-0.023142704436130434 +/- 0.0022807683905239715</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.00010689470871192431 +/- 0.00021378941742384862</t>
+          <t>0.00016034206306788645 +/- 0.0002449265470313243</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.004061998931052935 +/- 0.0013563418001549517</t>
+          <t>-0.00048102618920363714 +/- 0.000808805235190894</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>-0.0021913415285943596 +/- 0.0018273993583408775</t>
+          <t>0.0006413682522715236 +/- 0.0005756456234243116</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>-0.0028327097808658608 +/- 0.0012199585473557835</t>
+          <t>-5.344735435598435e-05 +/- 0.0009694472018822524</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>-0.00021378941742384862 +/- 0.0006413682522714996</t>
+          <t>0.0004275788348476639 +/- 0.0005236749850952676</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.0011223944414751163 +/- 0.0003741314804917002</t>
+          <t>0.0005879208979155393 +/- 0.0006070452534259912</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.00042757883484769723 +/- 0.0003999633764590203</t>
+          <t>-5.3447354355962154e-05 +/- 0.00028782281171217444</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>-0.0013896312132549826 +/- 0.0013351144838906267</t>
+          <t>0.0006948156066274635 +/- 0.0010432507373566654</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0.002137894174238353 +/- 0.0014927033718619906</t>
+          <t>-0.002030999465526484 +/- 0.0012827365045430252</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>-0.008711918760021397 +/- 0.000863468435136473</t>
+          <t>-0.0035275253874933353 +/- 0.0011262056390008383</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-0.007536076964190297 +/- 0.0014029294225982626</t>
+          <t>-0.004756814537680387 +/- 0.0011574777032446644</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.00037413148049170175 +/- 0.0006346521692697849</t>
+          <t>0.00048102618920364826 +/- 0.00028782281171215173</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.00016034206306788645 +/- 0.00041743718203672147</t>
+          <t>-0.00042757883484769723 +/- 0.0004659432328744949</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.004115446285408886 +/- 0.000927276941362786</t>
+          <t>-0.004970603955104247 +/- 0.0009272769413627649</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.0005344735435595771 +/- 0.00086181269356478</t>
+          <t>-0.0014965259219668736 +/- 0.0011160135231331357</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -3731,107 +3731,107 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-0.002779262426509899 +/- 0.0010901164112437796</t>
+          <t>-0.00010689470871193541 +/- 0.0005756456234243261</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-0.0012827365045430471 +/- 0.0008684167188280035</t>
+          <t>0.0010154997327632253 +/- 0.0016808321959932045</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>-0.00855157669695351 +/- 0.0017726482043588236</t>
+          <t>0.0014965259219668515 +/- 0.0009195430536657118</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-0.00016034206306788645 +/- 0.00048102618920365937</t>
+          <t>0.00026723677177978853 +/- 0.0005476724086563079</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.1102230246251566e-17 +/- 0.0005854864323946291</t>
+          <t>0.0005879208979155282 +/- 0.000652408103459829</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.0026723677177979744 +/- 0.0013308283910196332</t>
+          <t>-0.0025654730090860613 +/- 0.0013478909901569725</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.000908605024051301 +/- 0.0013102779980899287</t>
+          <t>0.001817210048102602 +/- 0.0009620523784072756</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.001282736504543003 +/- 0.0016069798373461181</t>
+          <t>0.002191341528594337 +/- 0.0014430785676108958</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>-0.011384286477819361 +/- 0.0018828343082638785</t>
+          <t>-0.006306787814003223 +/- 0.0017368334376560036</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-0.000748262960983448 +/- 0.0004898530940626098</t>
+          <t>-5.3447354355962154e-05 +/- 0.00044396706910307355</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-0.0015499732763228137 +/- 0.00044396706910303615</t>
+          <t>-0.0012292891501870852 +/- 0.0006781709000774662</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-0.0018706574024585864 +/- 0.0004927602596094435</t>
+          <t>0.00048102618920364826 +/- 0.00028782281171215173</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>-5.344735435597325e-05 +/- 0.0006524081034598599</t>
+          <t>-0.0019241047568145596 +/- 0.0009913007477814861</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>-0.0012292891501870739 +/- 0.000986968750006387</t>
+          <t>-0.0027258150721539364 +/- 0.0009694472018822487</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-5.344735435597325e-05 +/- 0.0015388754728902219</t>
+          <t>-0.0016568679850347489 +/- 0.0006948156066274712</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-0.006360235168359163 +/- 0.0024075052120909016</t>
+          <t>-0.0039016568679850483 +/- 0.00219134152859434</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-0.00042757883484769723 +/- 0.00039996337645902035</t>
+          <t>0.00016034206306788645 +/- 0.0002449265470313243</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.00033803074934992447</t>
+          <t>-0.00016034206306788645 +/- 0.0002449265470313243</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.0012292891501870518 +/- 0.0005879208979155443</t>
+          <t>-0.0005344735435596215 +/- 0.00033803074934992447</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.003848209513629075 +/- 0.0013048162069196787</t>
+          <t>-0.0006948156066274858 +/- 0.001852241950952803</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.0031533939070016006 +/- 0.0012292891501870596</t>
+          <t>-0.005184393372528085 +/- 0.001172191993557528</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3841,42 +3841,42 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>-0.0005879208979155725 +/- 0.0005580067615665801</t>
+          <t>0.00026723677177979964 +/- 0.0003585357526723278</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>-0.001175841795831123 +/- 0.0005236749850952609</t>
+          <t>-0.0011223944414751718 +/- 0.00037413148049169226</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-0.016622127204703373 +/- 0.0013189698214060152</t>
+          <t>0.0035809727418492756 +/- 0.0009869687500063894</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>-0.00010689470871192431 +/- 0.00021378941742384862</t>
+          <t>0.0002137894174238375 +/- 0.000427578834847675</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-0.0033137359700694978 +/- 0.0006675572419453009</t>
+          <t>0.0002137894174238153 +/- 0.000763380911656106</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-0.011277391769107437 +/- 0.001132529134175133</t>
+          <t>5.344735435595105e-05 +/- 0.0012523115461101127</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-0.00026723677177982187 +/- 0.0009635358833415235</t>
+          <t>-0.0031533939070016114 +/- 0.0006948156066274619</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-0.00048102618920364826 +/- 0.0005580067615665779</t>
+          <t>-0.0004810261892036705 +/- 0.0006524081034598526</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3886,47 +3886,47 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>-0.0005879208979155837 +/- 0.0003741314804917351</t>
+          <t>-0.0006413682522715458 +/- 0.0005756456234243489</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>-5.344735435595105e-05 +/- 0.0009395187510019923</t>
+          <t>-0.000748262960983459 +/- 0.0004898530940626292</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-0.0012292891501870852 +/- 0.0006346521692697859</t>
+          <t>0.0005879208979155503 +/- 0.0005042213325524467</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>-0.0013896312132549605 +/- 0.000724995187934277</t>
+          <t>-0.0007482629609834368 +/- 0.0009007108255666891</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>-0.002993051843933747 +/- 0.0011262056390008235</t>
+          <t>-0.0003206841261357729 +/- 0.0006413682522715458</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>0.0003206841261357618 +/- 0.000595164549741324</t>
+          <t>-0.000748262960983459 +/- 0.0005951645497413221</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>-5.3447354355962154e-05 +/- 0.0003741314804917351</t>
+          <t>5.3447354355962154e-05 +/- 0.00016034206306788645</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>-0.0003206841261357729 +/- 0.0007633809116561044</t>
+          <t>-5.3447354355962154e-05 +/- 0.00016034206306788645</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>0.00016034206306786425 +/- 0.000829726066074832</t>
+          <t>0.00026723677177981076 +/- 0.00026723677177981076</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>-0.00010689470871192431 +/- 0.00021378941742384862</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>-5.3447354355962154e-05 +/- 0.00028782281171217444</t>
+          <t>0.0011223944414751386 +/- 0.0006948156066274705</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -3951,37 +3951,37 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>-0.00042757883484769723 +/- 0.0003206841261357729</t>
+          <t>0.00026723677177981076 +/- 0.00035853575267235255</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>-0.001068947087119221 +/- 0.0003380307493498894</t>
+          <t>0.0002137894174238375 +/- 0.000427578834847675</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>-0.0019241047568145596 +/- 0.0006413682522715014</t>
+          <t>-0.00016034206306788645 +/- 0.0008297260660748349</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>-5.3447354355962154e-05 +/- 0.00016034206306788645</t>
+          <t>0.00016034206306788645 +/- 0.0002449265470313243</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>0.00026723677177978853 +/- 0.0005476724086563079</t>
+          <t>-0.0008551576696953722 +/- 0.0006413682522715199</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>-0.0006413682522715236 +/- 0.0006232979043126972</t>
+          <t>-0.001603420630678787 +/- 0.0007927523770278671</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>0.0011758417958310896 +/- 0.0009195430536657055</t>
+          <t>0.0008017103153393768 +/- 0.0005975595877872096</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0008551576696953167 +/- 0.0006413682522715013</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4001,27 +4001,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.0005344735435595438 +/- 0.0004140014266389327</t>
+          <t>0.00016034206306788645 +/- 0.0004810261892036594</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0001068947087119021 +/- 0.0002137894174238042</t>
+          <t>-0.0010154997327632587 +/- 0.0005042213325524526</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.0034740780331373733 +/- 0.0005476724086562917</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0002137894174238264 +/- 0.0005450582056218838</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.008177445216461743 +/- 0.0008297260660748105</t>
+          <t>0.001282736504543003 +/- 0.0004898530940626146</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4031,127 +4031,127 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.0009620523784072077 +/- 0.00032068412613577284</t>
+          <t>-0.00026723677177981076 +/- 0.0009927405462857532</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.009032602886157093 +/- 0.0012971310635501263</t>
+          <t>0.0025654730090860613 +/- 0.0005236749850952947</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.011972207375734867 +/- 0.0010473499701905465</t>
+          <t>0.0029396044895777405 +/- 0.0007269626140425031</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0005879208979155393 +/- 0.0005580067615665514</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.0004275788348476417 +/- 0.0005756456234242973</t>
+          <t>-0.0005344735435596105 +/- 0.0006760614986998314</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.00016034206306786425 +/- 0.00034223005010328183</t>
+          <t>-0.00037413148049173504 +/- 0.0005879208979155837</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.011010154997327593 +/- 0.0010473499701905658</t>
+          <t>0.00374131480491714 +/- 0.0010689470871191877</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-0.0007482629609834701 +/- 0.0008684167188280062</t>
+          <t>-0.004222340994120799 +/- 0.0017310673159488539</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.004115446285408897 +/- 0.0009575880741405143</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.001282736504543003 +/- 0.00042757883484765836</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.002725815072153892 +/- 0.0006948156066274618</t>
+          <t>0.0014965259219668291 +/- 0.00032068412613577284</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.0010689470871192096 +/- 0.0008943452982726622</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0005344735435596105 +/- 0.0002390238351148769</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.0009086050240513565 +/- 0.0005879208979155837</t>
+          <t>-0.007642971672902199 +/- 0.00154997327632282</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.00016034206306789756 +/- 0.0005879208979155604</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0012827365045429916 +/- 0.00035452964087176404</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.00042757883484769723 +/- 0.00032068412613577284</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.00048102618920363714 +/- 0.0003741314804917001</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.00016034206306785314 +/- 0.0002449265470312734</t>
+          <t>0.00026723677177979964 +/- 0.00043090634678239343</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0.0016568679850347046 +/- 0.0006070452534260175</t>
+          <t>-0.00048102618920363714 +/- 0.000607045253425995</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0.0060395510422233565 +/- 0.0008959409200556026</t>
+          <t>-0.0022447888829503215 +/- 0.000821073837292219</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>0.0016568679850347157 +/- 0.0005042213325524903</t>
+          <t>0.0003206841261357618 +/- 0.00042757883484767777</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-5.3447354355962154e-05 +/- 0.0005042213325524902</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>5.344735435595105e-05 +/- 0.00016034206306785314</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0009086050240512788 +/- 0.00024492654703127343</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -4161,72 +4161,72 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.00026723677177975524 +/- 0.00026723677177975524</t>
+          <t>-5.344735435597325e-05 +/- 0.0006070452534260156</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.0011758417958310564 +/- 0.0004659432328744949</t>
+          <t>-0.0017103153393907 +/- 0.000887934138206111</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0 +/- 0.00033803074934992447</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.00010689470871192431 +/- 0.00021378941742384862</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.00037413148049166847 +/- 0.00034223005010327484</t>
+          <t>-5.344735435597325e-05 +/- 0.0005042213325524655</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>0.0002137894174238042 +/- 0.00026183749254759983</t>
+          <t>-0.0003206841261357729 +/- 0.0002618374925476542</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.00016034206306788645 +/- 0.0002449265470313243</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.00021378941742384862 +/- 0.00035452964087178746</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>5.344735435595105e-05 +/- 0.00016034206306785314</t>
+          <t>-0.00026723677177981076 +/- 0.0004927602596094797</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.0064136825227151025 +/- 0.0010953448173126213</t>
+          <t>0.0011223944414750942 +/- 0.00016034206306788642</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.00048102618920359275 +/- 0.0004439670691030254</t>
+          <t>0.0006948156066274525 +/- 0.0005371392635553437</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.00481026189203636 +/- 0.0012420042799168745</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.0009086050240513455 +/- 0.00041743718203670303</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>0.0002137894174238042 +/- 0.00026183749254759983</t>
+          <t>0.0008017103153393878 +/- 0.0004927602596094315</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -4236,142 +4236,142 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0010154997327632032 +/- 0.0005042213325524467</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0011758417958310674 +/- 0.0003206841261357507</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.000962052378407241 +/- 0.0003206841261357285</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
+          <t>0.0004275788348476861 +/- 0.0005236749850952835</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0.0005344735435596215 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>-0.0024585783003741478 +/- 0.000962052378407257</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>0.000962052378407241 +/- 0.0005756456234243035</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>0.00026723677177979964 +/- 0.0003585357526723278</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>0.000427578834847675 +/- 0.00039996337645898473</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>0.0011758417958310674 +/- 0.00046594323287446686</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>0.00048102618920362603 +/- 0.0004439670691030294</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>-0.00042757883484769723 +/- 0.0004659432328744949</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>0.0012292891501870296 +/- 0.00034223005010330086</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>-0.0018706574024586087 +/- 0.0007652496559741435</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>-0.0007482629609834701 +/- 0.0003545296408717875</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>0.00016034206306786425 +/- 0.0005879208979155493</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>0.0009620523784072521 +/- 0.0003999633764589729</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>0.00048102618920363714 +/- 0.0003741314804917001</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>0.00021378941742384862 +/- 0.0002618374925476542</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>0.0003206841261357729 +/- 0.0003545296408717875</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>0.0005344735435595771 +/- 0.0004780476702297538</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
           <t>-0.00026723677177981076 +/- 0.00026723677177981076</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>0.0007482629609833924 +/- 0.0005951645497413061</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>0.0001068947087119021 +/- 0.0002137894174238042</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>-0.00026723677177981076 +/- 0.00026723677177981076</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0007482629609834146 +/- 0.0006413682522714996</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.00016034206306787536 +/- 0.0004174371820366974</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>0.0003206841261357174 +/- 0.00035452964087173726</t>
+          <t>0.0010689470871191654 +/- 0.00041400142663893273</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4396,37 +4396,37 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.00048102618920365937 +/- 0.00016034206306788645</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.00037413148049173504 +/- 0.0002449265470313243</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>0.000641368252271457 +/- 0.00039996337645898473</t>
+          <t>0.00048102618920364826 +/- 0.00028782281171215173</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.000374131480491724 +/- 0.00041743718203670303</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>0.0002137894174238042 +/- 0.00026183749254759983</t>
+          <t>-0.000374131480491724 +/- 0.000537139263555368</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>0.0001068947087119021 +/- 0.0002137894174238042</t>
+          <t>0.00021378941742384862 +/- 0.0004898530940626486</t>
         </is>
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>-0.00016034206306788645 +/- 0.0002449265470313243</t>
+          <t>0.0004275788348476861 +/- 0.00039996337645900257</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.0008358208955223878 +/- 0.0010746268656716513</t>
+          <t>-0.0017313432835820652 +/- 0.001146828221629763</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4446,432 +4446,432 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.003343283582089562 +/- 0.000716417910447766</t>
+          <t>-0.008537313432835791 +/- 0.0013093559522066435</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.0005373134328358175 +/- 0.001739558481711458</t>
+          <t>-0.005492537313432822 +/- 0.001302532789807243</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.00035820895522387097 +/- 0.0004776119402984947</t>
+          <t>-0.0013134328358208713 +/- 0.0009918356851245384</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.0007761194029850538 +/- 0.0010007793799546125</t>
+          <t>-0.0054925373134328105 +/- 0.001157654891323293</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.00047761194029849463 +/- 0.0004467650611073243</t>
+          <t>-0.002268656716417905 +/- 0.001126445508305283</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>5.970149253731183e-05 +/- 0.00017910447761193549</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.0013134328358208936 +/- 0.0006962330620711039</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.018507462686567187 +/- 0.0030206831380713032</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0.01886567164179106 +/- 0.00280279273893862</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0.0005373134328358175 +/- 0.0006780786084537662</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>-0.005910447761194015 +/- 0.0019701492537313285</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0.0018507462686567333 +/- 0.0016980850929346725</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>-0.005373134328358198 +/- 0.0017303136413360403</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>-0.0020298507462686356 +/- 0.0019474037528716677</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0.001552238805970163 +/- 0.0009700344363744648</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>-0.001074626865671624 +/- 0.0010612769453511065</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>0.00119402985074627 +/- 0.0009626576415879021</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>0.003164179104477638 +/- 0.000708915945494782</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>5.970149253731183e-05 +/- 0.00017910447761193549</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>-5.970149253731183e-05 +/- 0.0005632227541526179</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0.0010746268656716463 +/- 0.000584952774396008</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0.0005373134328358175 +/- 0.0006233018811289937</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0.0008358208955223767 +/- 0.0005471732173081647</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>0.0011343283582089692 +/- 0.0008630944653612697</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>-0.0011343283582089247 +/- 0.0004959178425622599</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>0.002746268656716444 +/- 0.001107297730805443</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>-0.001731343283582043 +/- 0.0007287495889990076</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>-0.0015522388059701075 +/- 0.0004776119402984946</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>-0.0015522388059701186 +/- 0.0006648076851140385</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>-0.0009552238805969893 +/- 0.0005471732173081453</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>-0.0013134328358208602 +/- 0.00035820895522387097</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>-0.00017910447761193549 +/- 0.00027358660865407265</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>0.0005970149253731183 +/- 0.0007063975860417262</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>-0.0016119402985074194 +/- 0.0006567164179104301</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>0.00017910447761193549 +/- 0.00046628356274068327</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0.00029850746268655914 +/- 0.0006674829783581282</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>-0.001074626865671613 +/- 0.0009171517310887643</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>-0.0033432835820895513 +/- 0.0008935301222146797</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-0.006388059701492499 +/- 0.0008875264923772347</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>0.0022686567164179384 +/- 0.0007456714027938505</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>0.010149253731343311 +/- 0.0011637963396786966</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>0.0026268656716418094 +/- 0.0009325671254814006</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>0.00017910447761193549 +/- 0.00027358660865407265</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>0.0010149253731343345 +/- 0.0009268163997767351</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>0.003343283582089562 +/- 0.001006107435603144</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>0.002985074626865691 +/- 0.001194029850746253</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-0.005671641791044746 +/- 0.00160751188272673</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>0.00011940298507462366 +/- 0.00023880597014924732</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
           <t>-0.00011940298507462366 +/- 0.00023880597014924732</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0.0063880597014925435 +/- 0.0015115210628265292</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.018208955223880607 +/- 0.003093551381022475</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>0.018686567164179102 +/- 0.0030796944182755657</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>-0.0007164179104477419 +/- 0.0005204655454973798</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>-0.0016119402985074528 +/- 0.0009268163997767353</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>-5.970149253731183e-05 +/- 0.0012650519462935237</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>-0.0011940298507462587 +/- 0.0016673719455246368</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>-0.00119402985074627 +/- 0.0009248915453629833</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0.0013731343283581831 +/- 0.0005373134328358275</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>5.970149253731183e-05 +/- 0.0010828869938636757</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>0.003522388059701509 +/- 0.0008207598259622179</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>-0.0011343283582089358 +/- 0.0009034475194281438</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>-5.970149253731183e-05 +/- 0.0005632227541526179</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>-0.0015522388059701297 +/- 0.0007645521477531883</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0.0016716417910447757 +/- 0.0007456714027938611</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0.0008955223880596774 +/- 0.0006117582546841387</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>5.970149253731183e-05 +/- 0.0006233018811289714</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>0.00011940298507462366 +/- 0.00023880597014924732</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>0.00483582089552238 +/- 0.0007761194029850785</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>-0.00011940298507462366 +/- 0.0007456714027938185</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>-0.0008358208955223656 +/- 0.0006088381508767341</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>-5.970149253731183e-05 +/- 0.0008207598259622179</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>-5.970149253731183e-05 +/- 0.00017910447761193549</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>-0.0009552238805969893 +/- 0.0007164179104477419</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>-0.0008358208955223656 +/- 0.0006648076851140146</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>0.00017910447761193549 +/- 0.00046628356274068327</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>0.00011940298507462366 +/- 0.00023880597014924734</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>0.001432835820895506 +/- 0.0009700344363744525</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>-0.0008955223880596774 +/- 0.000766879556935211</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>-0.0004179104477611828 +/- 0.00027358660865407265</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>0.0028656716417910454 +/- 0.0009171517310888034</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0.0007164179104477419 +/- 0.0008774291615939507</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>-0.0012537313432835484 +/- 0.00041791044776118286</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-0.0016119402985074415 +/- 0.0005999925743952896</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>0.002089552238805981 +/- 0.0008120280900737768</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>0.00262686567164182 +/- 0.000396014900340956</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>0.0005373134328358065 +/- 0.0004959178425622598</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>0.0020895522388059582 +/- 0.0008547952873598059</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>0.0008955223880596885 +/- 0.0007189011688831258</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>-0.005373134328358187 +/- 0.0008443066044018407</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>-0.0020895522388059695 +/- 0.0008547952873598097</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>-0.005731343283582069 +/- 0.0013924661241421562</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>0.006388059701492565 +/- 0.0007575270173402792</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>0.00017910447761193549 +/- 0.00027358660865407265</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>0.006029850746268661 +/- 0.0010828869938637217</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>-0.0035223880597014755 +/- 0.000820759825962264</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>-0.00023880597014924732 +/- 0.00039601490034093265</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>0.006208955223880619 +/- 0.0015150540346805439</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>0.006447761194029888 +/- 0.0008774291615939794</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>-0.0011940298507462366 +/- 0.0008443066044018251</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>0.0007164179104477419 +/- 0.00035820895522387097</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>0.00119402985074627 +/- 0.0004624457726815132</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>-0.00023880597014924732 +/- 0.0003960149003409326</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>0.00047761194029849463 +/- 0.0007920298006818652</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>-0.0015522388059701075 +/- 0.0004776119402984946</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>0.0008955223880596997 +/- 0.0007189011688831306</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>0.00047761194029849463 +/- 0.00023880597014924732</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>-5.970149253731183e-05 +/- 0.00041791044776118286</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>0.0019104477611940562 +/- 0.0008358208955224101</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>0.0007164179104477419 +/- 0.0004467650611073243</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>0.0016119402985074749 +/- 0.0005999925743953107</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>0.0009552238805969893 +/- 0.00029247638719798354</t>
         </is>
       </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0.00011940298507462366 +/- 0.00023880597014924732</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>0.0005970149253731183 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>-0.001074626865671635 +/- 0.0009552238805970197</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>0.0008955223880596774 +/- 0.0006117582546841387</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>0.0019701492537313346 +/- 0.0009268163997767417</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>0.0013134328358208824 +/- 0.0008774291615939855</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0.0020895522388059695 +/- 0.000971869886334336</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>0.00238805970149254 +/- 0.00110084112922902</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>-0.00017910447761193549 +/- 0.0003822760738765777</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>0.00023880597014924732 +/- 0.0004776119402984947</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>0.00023880597014924732 +/- 0.00047761194029849463</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>-0.00035820895522387097 +/- 0.00029247638719798354</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>0.00017910447761193549 +/- 0.00027358660865407265</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>0.002208955223880593 +/- 0.0006567164179104757</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>0.001552238805970141 +/- 0.0006088381508767798</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>0.0005970149253731183 +/- 0.00037758539225890087</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>5.970149253731183e-05 +/- 0.00017910447761193549</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>0.00017910447761193549 +/- 0.00027358660865407265</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>0.0007761194029850538 +/- 0.0005373134328358065</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>0.0004179104477611828 +/- 0.00027358660865407265</t>
-        </is>
-      </c>
-      <c r="CH10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CI10" t="inlineStr">
-        <is>
-          <t>0.0008955223880596774 +/- 0.0004813288207939303</t>
-        </is>
-      </c>
-      <c r="CJ10" t="inlineStr">
-        <is>
-          <t>5.970149253731183e-05 +/- 0.0003215023765453349</t>
-        </is>
-      </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>0.0018507462686567111 +/- 0.0008207598259622631</t>
+          <t>5.970149253732293e-05 +/- 0.0007761194029850786</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-0.0012137203166227239 +/- 0.0013150328015173775</t>
+          <t>0.0006860158311345566 +/- 0.0008192176620717725</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4891,157 +4891,157 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.2770448548788984e-05 +/- 0.0006441454150783158</t>
+          <t>0.00026385224274406706 +/- 0.0009215962636714</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.00026385224274411145 +/- 0.0012091228746585402</t>
+          <t>0.004063324538258561 +/- 0.0010567274086807712</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.00015831134564647797 +/- 0.0010827590780307925</t>
+          <t>0.0004221635883904895 +/- 0.0007755640346542827</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-0.0007387862796834454 +/- 0.0005381550937828951</t>
+          <t>0.00031662269129285604 +/- 0.0007897957544641611</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.001424802110818002 +/- 0.0012274093244973936</t>
+          <t>0.00026385224274404483 +/- 0.0009513327903598928</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.00047493403693940064 +/- 0.0001583113456464669</t>
+          <t>-5.277044854881119e-05 +/- 0.00015831134564643355</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.0005277044854881008 +/- 0.0005277044854881341</t>
+          <t>-0.0012137203166227128 +/- 0.001082759078030791</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.008390501319261157 +/- 0.0018945987410043448</t>
+          <t>0.015567282321899712 +/- 0.0020876032131770506</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.006754617414247976 +/- 0.0018249727140676388</t>
+          <t>0.01625329815303428 +/- 0.002297787974361723</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.0007915567282321456 +/- 0.0008259881711081142</t>
+          <t>0.003430079155672827 +/- 0.0007555578397507294</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.0017414248021107692 +/- 0.0007099537755711522</t>
+          <t>0.002638522427440626 +/- 0.0013760849404121727</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>-0.0005277044854882007 +/- 0.0008830184976613086</t>
+          <t>0.003641160949868072 +/- 0.0007985617915789802</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.01920844327176776 +/- 0.0021002373342619844</t>
+          <t>0.028759894459102896 +/- 0.0037851533172410215</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>-0.0021635883905013918 +/- 0.0016256381847756553</t>
+          <t>0.007810026385224256 +/- 0.0025830582059145836</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0.0006860158311345343 +/- 0.0006695819282559128</t>
+          <t>0.004854881266490763 +/- 0.0014700145938980533</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0.0011609498680738462 +/- 0.0007755640346542827</t>
+          <t>-0.0011609498680738906 +/- 0.000967298299726843</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0.0039050131926120835 +/- 0.0016720822710031467</t>
+          <t>0.011662269129287584 +/- 0.0013649094624145154</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>-0.0031662269129287936 +/- 0.0011561426015940061</t>
+          <t>-0.0010554089709762572 +/- 0.0005780713007970334</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.00010554089709762238 +/- 0.00021108179419524476</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.0029551451187334377 +/- 0.0007537127629068947</t>
+          <t>0.007124010554089688 +/- 0.0014785145885089098</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>-0.00031662269129292266 +/- 0.0005876268456813023</t>
+          <t>0.001899736147757225 +/- 0.0006757914762462251</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0.0004221635883904673 +/- 0.0006154038939150884</t>
+          <t>0.001899736147757236 +/- 0.0008893034061400011</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.0011081794195250349 +/- 0.0003693931398416783</t>
+          <t>0.000844327176780979 +/- 0.00048364914986339963</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.0005277044854881119 +/- 0.0004087581368028822</t>
+          <t>0.002269129287598937 +/- 0.0007481502310690366</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.00021108179419528916 +/- 0.0002585213448848153</t>
+          <t>5.277044854881119e-05 +/- 0.00015831134564643355</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>-0.0026385224274406817 +/- 0.0011799831015829893</t>
+          <t>0.005171503957783641 +/- 0.002392777635621029</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-0.0005804749340370119 +/- 0.00043834426717247486</t>
+          <t>-0.0037467018469657053 +/- 0.0009571692425971792</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>-0.0005277044854881785 +/- 0.0006243883676094876</t>
+          <t>-0.0011081794195250793 +/- 0.0006860158311345932</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-0.0013720316622692018 +/- 0.0005876268456812524</t>
+          <t>5.277044854881119e-05 +/- 0.0005993570813509356</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>-0.00010554089709765568 +/- 0.00031662269129291155</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.00042216358839055614 +/- 0.0005683551247635635</t>
+          <t>5.277044854881119e-05 +/- 0.00028417756238176007</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -5051,12 +5051,12 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.00036939313984174493 +/- 0.0003378957381231446</t>
+          <t>-0.002321899736147792 +/- 0.001006795990941359</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.0013720316622690908 +/- 0.0006332453825857342</t>
+          <t>0.0010026385224274127 +/- 0.0003693931398416783</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -5066,107 +5066,107 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-0.00010554089709764458 +/- 0.00021108179419528916</t>
+          <t>0.00026385224274405594 +/- 0.0003539949304748908</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-0.0005277044854881674 +/- 0.0008508979153877273</t>
+          <t>0.004116094986807373 +/- 0.0011752536913625237</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>0.00010554089709757797 +/- 0.0006591026911238747</t>
+          <t>0.0011081794195250349 +/- 0.0007628935247915861</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>0.0004221635883904895 +/- 0.00021108179419524476</t>
+          <t>-0.0017941952506596581 +/- 0.0005381550937829104</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.00010554089709765568 +/- 0.00031662269129291155</t>
+          <t>-0.0004221635883905117 +/- 0.0007387862796833915</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.00026385224274412257 +/- 0.0005407361881773157</t>
+          <t>-0.0010554089709762459 +/- 0.000471993240633225</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.000369393139841645 +/- 0.000945460309613153</t>
+          <t>-0.0031662269129287823 +/- 0.0010554089709762238</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-0.009182058047493436 +/- 0.0022413467632290416</t>
+          <t>-0.001002638522427457 +/- 0.0018499786958267068</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.0044327176781002176 +/- 0.0005381550937829104</t>
+          <t>0.0167810026385224 +/- 0.0006154038939150541</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-0.0014775725593668243 +/- 0.0007000791114206452</t>
+          <t>0.0011609498680738462 +/- 0.000659102691123823</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-0.0010554089709763237 +/- 0.0006243883676094594</t>
+          <t>-0.0016886543535620468 +/- 0.0006591026911238532</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.00031662269129286715 +/- 0.0003500395557103226</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>-0.0006332453825858119 +/- 0.0005683551247635572</t>
+          <t>-0.0005277044854881341 +/- 0.0009730389928541396</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>-0.005699208443271819 +/- 0.0011752536913625287</t>
+          <t>-0.003324538258575205 +/- 0.0012498912171321236</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-0.0029023746701847264 +/- 0.0016392849147239055</t>
+          <t>-0.006912928759894477 +/- 0.0019237705681855585</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-0.0034300791556728717 +/- 0.0015520254532826077</t>
+          <t>0.0013192612137203018 +/- 0.001254339242639022</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>0.0007387862796833566 +/- 0.0003500395557103226</t>
+          <t>-0.00021108179419524476 +/- 0.00025852134488476094</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>-0.0005277044854882007 +/- 0.0003337496211259761</t>
+          <t>0.0006332453825857343 +/- 0.0005170426897695218</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>-0.000580474934037023 +/- 0.00028417756238178273</t>
+          <t>5.277044854881119e-05 +/- 0.00028417756238176007</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-0.0015831134564644246 +/- 0.0013139735723470903</t>
+          <t>0.0007387862796833678 +/- 0.0019345965994536668</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.0011081794195250349 +/- 0.00043834426717244553</t>
+          <t>-0.0015831134564643912 +/- 0.000782712241382151</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5176,82 +5176,82 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>-2.2204460492503132e-17 +/- 0.000471993240633225</t>
+          <t>0.0 +/- 0.0002359966203165939</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>-0.0005804749340370119 +/- 0.0004978354159396862</t>
+          <t>0.0007387862796833566 +/- 0.0004221635883904895</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>-0.0034828496042216715 +/- 0.0014001582228413275</t>
+          <t>-0.0009498680738786458 +/- 0.001778606812279969</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>-0.00047493403693940064 +/- 0.00015831134564646686</t>
+          <t>5.277044854881119e-05 +/- 0.00015831134564643355</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.0004749340369392896 +/- 0.000550939657462303</t>
+          <t>0.0 +/- 0.0007827122413821061</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-0.0036939313984169276 +/- 0.0018879729625327914</t>
+          <t>-0.005857519788918219 +/- 0.0013234761165155187</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>0.011503957783641095 +/- 0.0012443088255991188</t>
+          <t>0.018575197889182028 +/- 0.0006591026911238693</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>0.0011609498680738462 +/- 0.00046004210485916115</t>
+          <t>0.0044327176781002505 +/- 0.0008893034061399602</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>5.277044854881119e-05 +/- 0.00015831134564643355</t>
+          <t>-0.00015831134564643358 +/- 0.00024182457493169982</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>0.0004221635883904784 +/- 0.0004600421048591841</t>
+          <t>0.0050659630606859855 +/- 0.0006332453825857342</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.0003693931398416783 +/- 0.00024182457493169984</t>
+          <t>0.0006332453825857343 +/- 0.0006154038939150541</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.0013192612137202687 +/- 0.0008590406647018313</t>
+          <t>0.0004749340369393007 +/- 0.0006860158311345455</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-0.00010554089709767789 +/- 0.0007387862796834042</t>
+          <t>0.004116094986807384 +/- 0.0005683551247635201</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>-0.0008443271767810901 +/- 0.0004221635883904895</t>
+          <t>-0.0006860158311345676 +/- 0.0005303364443863494</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>0.0013720316622690908 +/- 0.0004221635883904895</t>
+          <t>0.00242744063324537 +/- 0.001230807787830151</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.00010554089709762238 +/- 0.00021108179419524476</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>5.277044854881119e-05 +/- 0.00015831134564643355</t>
+          <t>-0.00026385224274405594 +/- 0.00026385224274405594</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>-0.00026385224274411145 +/- 0.0002638522427441115</t>
+          <t>0.0 +/- 0.0004087581368028822</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>0.0010554089709762238 +/- 0.00047199324063318783</t>
+          <t>0.006385224274406309 +/- 0.0014248021108179455</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5286,37 +5286,37 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>0.00010554089709762238 +/- 0.00021108179419524476</t>
+          <t>0.0005277044854881119 +/- 0.0006243883676094407</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>-0.0005804749340370008 +/- 0.0005993570813509776</t>
+          <t>0.002796833773087071 +/- 0.001181162495282296</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>0.00015831134564643358 +/- 0.000337895738123096</t>
+          <t>0.0005804749340369231 +/- 0.0007985617915789515</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>0.00010554089709762238 +/- 0.00021108179419524476</t>
+          <t>0.0016886543535619913 +/- 0.0009956708318793407</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>-0.0024802110817942367 +/- 0.0006695819282558925</t>
+          <t>0.0035356200527704384 +/- 0.0012498912171321334</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>0.0010026385224274127 +/- 0.00043834426717244553</t>
+          <t>0.005963060686015797 +/- 0.0009454603096131424</t>
         </is>
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>0.00015831134564642246 +/- 0.0004121503786758199</t>
+          <t>0.008232189973614756 +/- 0.0008574183012808408</t>
         </is>
       </c>
     </row>
